--- a/Excel/DungeonSectionConfig.xlsx
+++ b/Excel/DungeonSectionConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA5C455-80B6-4A3A-B091-A194508ACB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A36AF91-728D-42F4-951F-96F1E39DEFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{4AE5065B-D0CC-4FE5-9F20-2DA759B1B601}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{4AE5065B-D0CC-4FE5-9F20-2DA759B1B601}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -87,132 +87,181 @@
     <t>ChapterName</t>
   </si>
   <si>
+    <t>RandomArea</t>
+  </si>
+  <si>
+    <t>OpenLevel</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>初章</t>
+  </si>
+  <si>
+    <t>家园危机</t>
+  </si>
+  <si>
+    <t>10001,10002,10004,10007,10006</t>
+  </si>
+  <si>
+    <t>0,10,15</t>
+  </si>
+  <si>
+    <t>第二章</t>
+  </si>
+  <si>
+    <t>荒漠探险</t>
+  </si>
+  <si>
+    <t>20001,20002,20003,20004,20005</t>
+  </si>
+  <si>
+    <t>第三章</t>
+  </si>
+  <si>
+    <t>冰封世界</t>
+  </si>
+  <si>
+    <t>30001,30003,30004,30005,30006</t>
+  </si>
+  <si>
+    <t>30,33,35</t>
+  </si>
+  <si>
+    <t>第四章</t>
+  </si>
+  <si>
+    <t>暮色危境</t>
+  </si>
+  <si>
+    <t>40001,40003,40004,40006,40007</t>
+  </si>
+  <si>
+    <t>40,43,45</t>
+  </si>
+  <si>
+    <t>第五章</t>
+  </si>
+  <si>
+    <t>黑暗陨落</t>
+  </si>
+  <si>
+    <t>50001,50002,50004,50006,50007</t>
+  </si>
+  <si>
+    <t>50,53,55</t>
+  </si>
+  <si>
+    <t>终章</t>
+  </si>
+  <si>
+    <t>黎明之光</t>
+  </si>
+  <si>
+    <t>60,62,65</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘之门地图ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShenMiEnterID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100101@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100201@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100301@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100401@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100501@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100601@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,22,25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>60001,60002,60003</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChapterName_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>RandomArea</t>
-  </si>
-  <si>
-    <t>OpenLevel</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>初章</t>
-  </si>
-  <si>
-    <t>家园危机</t>
-  </si>
-  <si>
-    <t>10001,10002,10004,10007,10006</t>
-  </si>
-  <si>
-    <t>0,10,15</t>
-  </si>
-  <si>
-    <t>第二章</t>
-  </si>
-  <si>
-    <t>荒漠探险</t>
-  </si>
-  <si>
-    <t>20001,20002,20003,20004,20005</t>
-  </si>
-  <si>
-    <t>第三章</t>
-  </si>
-  <si>
-    <t>冰封世界</t>
-  </si>
-  <si>
-    <t>30001,30003,30004,30005,30006</t>
-  </si>
-  <si>
-    <t>30,33,35</t>
-  </si>
-  <si>
-    <t>第四章</t>
-  </si>
-  <si>
-    <t>暮色危境</t>
-  </si>
-  <si>
-    <t>40001,40003,40004,40006,40007</t>
-  </si>
-  <si>
-    <t>40,43,45</t>
-  </si>
-  <si>
-    <t>第五章</t>
-  </si>
-  <si>
-    <t>黑暗陨落</t>
-  </si>
-  <si>
-    <t>50001,50002,50004,50006,50007</t>
-  </si>
-  <si>
-    <t>50,53,55</t>
-  </si>
-  <si>
-    <t>终章</t>
-  </si>
-  <si>
-    <t>黎明之光</t>
-  </si>
-  <si>
-    <t>60,62,65</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>神秘之门地图ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShenMiEnterID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100101@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100201@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100301@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100401@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100501@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100601@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,22,25</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>60001,60002,60003</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter 1</t>
+  </si>
+  <si>
+    <t>Chapter Two</t>
+  </si>
+  <si>
+    <t>Chapter Three</t>
+  </si>
+  <si>
+    <t>Chapter 4</t>
+  </si>
+  <si>
+    <t>Chapter Five</t>
+  </si>
+  <si>
+    <t>Final Chapter</t>
+  </si>
+  <si>
+    <t>Home Crisis</t>
+  </si>
+  <si>
+    <t>Desert exploration</t>
+  </si>
+  <si>
+    <t>Frozen world</t>
+  </si>
+  <si>
+    <t>Dusk Crisis</t>
+  </si>
+  <si>
+    <t>Dark Descension</t>
+  </si>
+  <si>
+    <t>Dawn Light</t>
   </si>
 </sst>
 </file>
@@ -409,7 +458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -445,12 +494,94 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -494,12 +625,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C4:F5" totalsRowShown="0">
-  <autoFilter ref="C4:F5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C4:H5" totalsRowShown="0">
+  <autoFilter ref="C4:H5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ChapterName"/>
+    <tableColumn id="5" xr3:uid="{5A8D0423-0DC6-42DA-9FD5-5B9A60755106}" name="ChapterName_EN" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Name"/>
+    <tableColumn id="6" xr3:uid="{3F2C2060-6987-4958-A5B8-B7131B13E6B4}" name="Name_EN" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="RandomArea"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -793,15 +926,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:I20"/>
+  <dimension ref="C2:K20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="5" width="16.75" customWidth="1"/>
-    <col min="6" max="8" width="33.625" customWidth="1"/>
+    <col min="4" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="10" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:11" x14ac:dyDescent="0.15">
+      <c r="E2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -809,184 +950,238 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>35</v>
+      <c r="J3" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4" spans="3:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="J4" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="2"/>
     </row>
-    <row r="5" spans="3:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="3:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="6">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="G6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>37</v>
+      <c r="J6" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="7" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="8">
         <v>2</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="G7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>38</v>
+      <c r="I7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="3:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="6">
         <v>3</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="G8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="I8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>39</v>
+      <c r="J8" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="9" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="8">
         <v>4</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="I9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>40</v>
+      <c r="J9" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="10" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="8">
         <v>5</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="I10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>41</v>
+      <c r="J10" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="11" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="8">
         <v>6</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="G11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>42</v>
+      <c r="J11" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="12" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/Excel/DungeonSectionConfig.xlsx
+++ b/Excel/DungeonSectionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A36AF91-728D-42F4-951F-96F1E39DEFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701235C3-C1CE-4246-B039-37E214769508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonSectionProto" sheetId="1" r:id="rId1"/>
@@ -150,118 +150,119 @@
     <t>第五章</t>
   </si>
   <si>
+    <t>50001,50002,50004,50006,50007</t>
+  </si>
+  <si>
+    <t>50,53,55</t>
+  </si>
+  <si>
+    <t>终章</t>
+  </si>
+  <si>
+    <t>黎明之光</t>
+  </si>
+  <si>
+    <t>60,62,65</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘之门地图ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShenMiEnterID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100101@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100201@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100301@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100401@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100501@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100601@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,22,25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>60001,60002,60003</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChapterName_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter 1</t>
+  </si>
+  <si>
+    <t>Chapter 4</t>
+  </si>
+  <si>
+    <t>Final Chapter</t>
+  </si>
+  <si>
+    <t>Home Crisis</t>
+  </si>
+  <si>
+    <t>Frozen world</t>
+  </si>
+  <si>
+    <t>Dusk Crisis</t>
+  </si>
+  <si>
+    <t>Dawn Light</t>
+  </si>
+  <si>
+    <t>Chapter 2</t>
+  </si>
+  <si>
+    <t>Chapter 3</t>
+  </si>
+  <si>
+    <t>Chapter 5</t>
+  </si>
+  <si>
+    <t>Desert Land</t>
+  </si>
+  <si>
     <t>黑暗陨落</t>
-  </si>
-  <si>
-    <t>50001,50002,50004,50006,50007</t>
-  </si>
-  <si>
-    <t>50,53,55</t>
-  </si>
-  <si>
-    <t>终章</t>
-  </si>
-  <si>
-    <t>黎明之光</t>
-  </si>
-  <si>
-    <t>60,62,65</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>神秘之门地图ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShenMiEnterID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100101@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100201@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100301@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100401@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100501@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100601@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,22,25</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>60001,60002,60003</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChapterName_EN</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name_EN</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chapter 1</t>
-  </si>
-  <si>
-    <t>Chapter Two</t>
-  </si>
-  <si>
-    <t>Chapter Three</t>
-  </si>
-  <si>
-    <t>Chapter 4</t>
-  </si>
-  <si>
-    <t>Chapter Five</t>
-  </si>
-  <si>
-    <t>Final Chapter</t>
-  </si>
-  <si>
-    <t>Home Crisis</t>
-  </si>
-  <si>
-    <t>Desert exploration</t>
-  </si>
-  <si>
-    <t>Frozen world</t>
-  </si>
-  <si>
-    <t>Dusk Crisis</t>
-  </si>
-  <si>
-    <t>Dark Descension</t>
-  </si>
-  <si>
-    <t>Dawn Light</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Darkness Falls</t>
   </si>
 </sst>
 </file>
@@ -458,7 +459,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -495,6 +496,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -930,16 +934,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="7" width="16.75" customWidth="1"/>
+    <col min="4" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="7" width="24.625" customWidth="1"/>
     <col min="8" max="10" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:11" x14ac:dyDescent="0.15">
       <c r="E2" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +970,7 @@
         <v>4</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -976,13 +981,13 @@
         <v>5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>6</v>
@@ -991,7 +996,7 @@
         <v>7</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1017,7 +1022,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" s="2"/>
     </row>
@@ -1029,13 +1034,13 @@
         <v>11</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>13</v>
@@ -1044,7 +1049,7 @@
         <v>14</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1054,23 +1059,23 @@
       <c r="D7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>49</v>
+      <c r="E7" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>55</v>
+      <c r="G7" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1080,14 +1085,14 @@
       <c r="D8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>50</v>
+      <c r="E8" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>20</v>
@@ -1096,7 +1101,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1106,14 +1111,14 @@
       <c r="D9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>51</v>
+      <c r="E9" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>24</v>
@@ -1122,7 +1127,7 @@
         <v>25</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1132,23 +1137,23 @@
       <c r="D10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="10" t="s">
+      <c r="I10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="J10" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1156,25 +1161,25 @@
         <v>6</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="H11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="J11" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/Excel/DungeonSectionConfig.xlsx
+++ b/Excel/DungeonSectionConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701235C3-C1CE-4246-B039-37E214769508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9CC3F3-E1F3-4BEE-8245-CFDFAB280A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -162,107 +162,108 @@
     <t>黎明之光</t>
   </si>
   <si>
+    <t>string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘之门地图ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShenMiEnterID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100101@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100201@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100301@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100401@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100501@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100;100601@100;100001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,22,25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChapterName_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter 1</t>
+  </si>
+  <si>
+    <t>Chapter 4</t>
+  </si>
+  <si>
+    <t>Final Chapter</t>
+  </si>
+  <si>
+    <t>Home Crisis</t>
+  </si>
+  <si>
+    <t>Frozen world</t>
+  </si>
+  <si>
+    <t>Dusk Crisis</t>
+  </si>
+  <si>
+    <t>Dawn Light</t>
+  </si>
+  <si>
+    <t>Chapter 2</t>
+  </si>
+  <si>
+    <t>Chapter 3</t>
+  </si>
+  <si>
+    <t>Chapter 5</t>
+  </si>
+  <si>
+    <t>Desert Land</t>
+  </si>
+  <si>
+    <t>黑暗陨落</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Darkness Falls</t>
+  </si>
+  <si>
+    <t>60001,60002,60003</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>60,62,65</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>神秘之门地图ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShenMiEnterID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100101@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100201@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100301@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100401@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100501@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100;100601@100;100001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,22,25</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>60001,60002,60003</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChapterName_EN</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name_EN</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chapter 1</t>
-  </si>
-  <si>
-    <t>Chapter 4</t>
-  </si>
-  <si>
-    <t>Final Chapter</t>
-  </si>
-  <si>
-    <t>Home Crisis</t>
-  </si>
-  <si>
-    <t>Frozen world</t>
-  </si>
-  <si>
-    <t>Dusk Crisis</t>
-  </si>
-  <si>
-    <t>Dawn Light</t>
-  </si>
-  <si>
-    <t>Chapter 2</t>
-  </si>
-  <si>
-    <t>Chapter 3</t>
-  </si>
-  <si>
-    <t>Chapter 5</t>
-  </si>
-  <si>
-    <t>Desert Land</t>
-  </si>
-  <si>
-    <t>黑暗陨落</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Darkness Falls</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -459,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -497,6 +498,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -941,10 +945,10 @@
   <sheetData>
     <row r="2" spans="3:11" x14ac:dyDescent="0.15">
       <c r="E2" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -970,7 +974,7 @@
         <v>4</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -981,13 +985,13 @@
         <v>5</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>6</v>
@@ -996,7 +1000,7 @@
         <v>7</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1022,7 +1026,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K5" s="2"/>
     </row>
@@ -1034,13 +1038,13 @@
         <v>11</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>13</v>
@@ -1049,7 +1053,7 @@
         <v>14</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1060,22 +1064,22 @@
         <v>15</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="3:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1086,13 +1090,13 @@
         <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>20</v>
@@ -1101,7 +1105,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1112,13 +1116,13 @@
         <v>22</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>24</v>
@@ -1127,7 +1131,7 @@
         <v>25</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1138,13 +1142,13 @@
         <v>26</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>58</v>
-      </c>
       <c r="G10" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>27</v>
@@ -1153,7 +1157,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1164,22 +1168,22 @@
         <v>29</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>31</v>
+        <v>58</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/Excel/DungeonSectionConfig.xlsx
+++ b/Excel/DungeonSectionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9CC3F3-E1F3-4BEE-8245-CFDFAB280A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE540111-034C-4704-AA20-50E2E5AECF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonSectionProto" sheetId="1" r:id="rId1"/>
@@ -258,11 +258,11 @@
     <t>Darkness Falls</t>
   </si>
   <si>
-    <t>60001,60002,60003</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>60,62,65</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>60001,60002,60003,60004</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1177,10 +1177,10 @@
         <v>51</v>
       </c>
       <c r="H11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>58</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>59</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>39</v>

--- a/Excel/DungeonSectionConfig.xlsx
+++ b/Excel/DungeonSectionConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE540111-034C-4704-AA20-50E2E5AECF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F55F76-03D8-41DD-A16E-C0D60589AFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
